--- a/source_data/Figure6.xlsx
+++ b/source_data/Figure6.xlsx
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>761.6208923809667</v>
+        <v>760.7249254466265</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -755,7 +755,7 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>67.25001813808062</v>
+        <v>18.1468302912281</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -784,10 +784,10 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>72.13933769774226</v>
+        <v>10.65360682863999</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -813,7 +813,7 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>366.3319961252419</v>
+        <v>367.2606063018525</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -842,10 +842,10 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>135.6988243144004</v>
+        <v>113.6830247105905</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
         <v>27</v>
@@ -871,10 +871,10 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>37.11232094043599</v>
+        <v>24.91581898666</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -900,7 +900,7 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>224.7380761411263</v>
+        <v>224.353388997563</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -929,7 +929,7 @@
         <v>33</v>
       </c>
       <c r="D9">
-        <v>52.32549498306765</v>
+        <v>14.88354558446479</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -958,7 +958,7 @@
         <v>33</v>
       </c>
       <c r="D10">
-        <v>28.90000634733787</v>
+        <v>9.990325118339383</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -987,7 +987,7 @@
         <v>35</v>
       </c>
       <c r="D11">
-        <v>129.4391267822657</v>
+        <v>129.5997411597099</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1016,7 +1016,7 @@
         <v>35</v>
       </c>
       <c r="D12">
-        <v>10.89184498677155</v>
+        <v>4.173783617492655</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1045,10 +1045,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>19.81032332703572</v>
+        <v>13.52957110361621</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="s">
         <v>29</v>
@@ -1074,7 +1074,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>396.9867302289278</v>
+        <v>397.3376949619366</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1103,10 +1103,10 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>153.3787802251116</v>
+        <v>123.0875237166268</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="s">
         <v>27</v>
@@ -1132,10 +1132,10 @@
         <v>37</v>
       </c>
       <c r="D16">
-        <v>53.95343031697146</v>
+        <v>41.34335787242581</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -1161,7 +1161,7 @@
         <v>39</v>
       </c>
       <c r="D17">
-        <v>268.3271256090866</v>
+        <v>268.3843488563369</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -1190,10 +1190,10 @@
         <v>39</v>
       </c>
       <c r="D18">
-        <v>324.9365537246113</v>
+        <v>214.9518090430962</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -1219,7 +1219,7 @@
         <v>39</v>
       </c>
       <c r="D19">
-        <v>26.80010861770792</v>
+        <v>7.645624680572847</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -1248,7 +1248,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>1693.713085159807</v>
+        <v>1693.572377630412</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -1277,7 +1277,7 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>27.21449156777539</v>
+        <v>12.59228926670447</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1306,7 +1306,7 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>15.91224391933893</v>
+        <v>2.618608506616466</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1335,7 +1335,7 @@
         <v>43</v>
       </c>
       <c r="D23">
-        <v>1129.496421154182</v>
+        <v>1105.442682633964</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -1364,7 +1364,7 @@
         <v>43</v>
       </c>
       <c r="D24">
-        <v>170.6191924335079</v>
+        <v>74.47665136494027</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -1393,10 +1393,10 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>67.56294097297004</v>
+        <v>12.99472341907263</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
         <v>29</v>
@@ -1422,7 +1422,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>1782.370173642894</v>
+        <v>1783.747283001748</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -1451,10 +1451,10 @@
         <v>45</v>
       </c>
       <c r="D27">
-        <v>62.71252183793935</v>
+        <v>47.19195464795877</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="s">
         <v>27</v>
@@ -1480,10 +1480,10 @@
         <v>45</v>
       </c>
       <c r="D28">
-        <v>31.53903856718597</v>
+        <v>20.79026595101068</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="s">
         <v>29</v>
@@ -1509,7 +1509,7 @@
         <v>47</v>
       </c>
       <c r="D29">
-        <v>115.6159125568454</v>
+        <v>115.9169175023088</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1538,10 +1538,10 @@
         <v>47</v>
       </c>
       <c r="D30">
-        <v>51.40529400277442</v>
+        <v>36.89137490555263</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="s">
         <v>27</v>
@@ -1567,10 +1567,10 @@
         <v>47</v>
       </c>
       <c r="D31">
-        <v>19.45962174161331</v>
+        <v>9.261991768428196</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="s">
         <v>29</v>
@@ -1596,7 +1596,7 @@
         <v>49</v>
       </c>
       <c r="D32">
-        <v>657.6704961572924</v>
+        <v>657.7101841964064</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -1625,10 +1625,10 @@
         <v>49</v>
       </c>
       <c r="D33">
-        <v>294.4720208791497</v>
+        <v>227.7820589871915</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" t="s">
         <v>27</v>
@@ -1654,10 +1654,10 @@
         <v>49</v>
       </c>
       <c r="D34">
-        <v>98.44700785630522</v>
+        <v>72.69112413964704</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
         <v>29</v>
@@ -1683,7 +1683,7 @@
         <v>51</v>
       </c>
       <c r="D35">
-        <v>935.8299155109588</v>
+        <v>935.9543755315033</v>
       </c>
       <c r="E35">
         <v>4</v>
@@ -1712,10 +1712,10 @@
         <v>51</v>
       </c>
       <c r="D36">
-        <v>498.3658184716266</v>
+        <v>114.3111642140532</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="s">
         <v>27</v>
@@ -1741,10 +1741,10 @@
         <v>51</v>
       </c>
       <c r="D37">
-        <v>51.25499690888518</v>
+        <v>9.403169138378297</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37" t="s">
         <v>29</v>
@@ -1770,7 +1770,7 @@
         <v>53</v>
       </c>
       <c r="D38">
-        <v>1538.67095069796</v>
+        <v>1538.9896816228</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -1799,10 +1799,10 @@
         <v>53</v>
       </c>
       <c r="D39">
-        <v>196.5821881713077</v>
+        <v>155.9401117997334</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="s">
         <v>27</v>
@@ -1828,10 +1828,10 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>13.80639958278007</v>
+        <v>6.939301534230723</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="s">
         <v>29</v>
@@ -1857,7 +1857,7 @@
         <v>55</v>
       </c>
       <c r="D41">
-        <v>105.8284781199683</v>
+        <v>106.0508645065856</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1886,10 +1886,10 @@
         <v>55</v>
       </c>
       <c r="D42">
-        <v>57.78838556090096</v>
+        <v>28.80723400106806</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="s">
         <v>27</v>
@@ -1915,10 +1915,10 @@
         <v>55</v>
       </c>
       <c r="D43">
-        <v>13.81219038420153</v>
+        <v>6.937813763268943</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="s">
         <v>29</v>
@@ -1944,7 +1944,7 @@
         <v>57</v>
       </c>
       <c r="D44">
-        <v>357.9410575011049</v>
+        <v>358.2471900781778</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -1973,10 +1973,10 @@
         <v>57</v>
       </c>
       <c r="D45">
-        <v>177.5011666846259</v>
+        <v>131.1837535976336</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" t="s">
         <v>27</v>
@@ -2002,7 +2002,7 @@
         <v>57</v>
       </c>
       <c r="D46">
-        <v>31.85785010194586</v>
+        <v>15.4782711480731</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -2031,7 +2031,7 @@
         <v>59</v>
       </c>
       <c r="D47">
-        <v>1212.045814592163</v>
+        <v>1212.290285512076</v>
       </c>
       <c r="E47">
         <v>4</v>
@@ -2060,7 +2060,7 @@
         <v>59</v>
       </c>
       <c r="D48">
-        <v>20.45328340547615</v>
+        <v>9.357281171826848</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         <v>59</v>
       </c>
       <c r="D49">
-        <v>4.702669778896399</v>
+        <v>0.6524448268638271</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -2118,7 +2118,7 @@
         <v>61</v>
       </c>
       <c r="D50">
-        <v>264.4868870666639</v>
+        <v>264.7755914388144</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -2147,7 +2147,7 @@
         <v>61</v>
       </c>
       <c r="D51">
-        <v>194.4231476852588</v>
+        <v>99.65401283102314</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -2176,10 +2176,10 @@
         <v>61</v>
       </c>
       <c r="D52">
-        <v>25.55803571858191</v>
+        <v>2.055254347076264</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="s">
         <v>29</v>
@@ -2205,7 +2205,7 @@
         <v>63</v>
       </c>
       <c r="D53">
-        <v>315.147738113812</v>
+        <v>315.742931686186</v>
       </c>
       <c r="E53">
         <v>2</v>
@@ -2234,10 +2234,10 @@
         <v>63</v>
       </c>
       <c r="D54">
-        <v>94.90797018994768</v>
+        <v>75.87266356128049</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="s">
         <v>27</v>
@@ -2263,7 +2263,7 @@
         <v>63</v>
       </c>
       <c r="D55">
-        <v>6.172081461636783</v>
+        <v>2.005149077662273</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -2292,7 +2292,7 @@
         <v>65</v>
       </c>
       <c r="D56">
-        <v>581.861334118146</v>
+        <v>582.0425431565758</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -2321,10 +2321,10 @@
         <v>65</v>
       </c>
       <c r="D57">
-        <v>264.1619171688866</v>
+        <v>202.5028770043829</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="s">
         <v>27</v>
@@ -2350,10 +2350,10 @@
         <v>65</v>
       </c>
       <c r="D58">
-        <v>69.57627624060105</v>
+        <v>36.86804480404135</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="s">
         <v>29</v>
@@ -2379,7 +2379,7 @@
         <v>67</v>
       </c>
       <c r="D59">
-        <v>361.3806737189068</v>
+        <v>360.9791588770014</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -2408,7 +2408,7 @@
         <v>67</v>
       </c>
       <c r="D60">
-        <v>5.639064915764338</v>
+        <v>1.690204324382488</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>67</v>
       </c>
       <c r="D61">
-        <v>2.347076112238387</v>
+        <v>0.4231598468599666</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -2466,7 +2466,7 @@
         <v>69</v>
       </c>
       <c r="D62">
-        <v>293.8994321615687</v>
+        <v>293.9001375395331</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -2495,10 +2495,10 @@
         <v>69</v>
       </c>
       <c r="D63">
-        <v>105.898746505972</v>
+        <v>88.07331630847186</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
@@ -2524,10 +2524,10 @@
         <v>69</v>
       </c>
       <c r="D64">
-        <v>50.76367145760086</v>
+        <v>42.66549156340798</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" t="s">
         <v>29</v>
@@ -2553,7 +2553,7 @@
         <v>71</v>
       </c>
       <c r="D65">
-        <v>277.3645721203505</v>
+        <v>277.6387050865425</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -2582,7 +2582,7 @@
         <v>71</v>
       </c>
       <c r="D66">
-        <v>119.8505813666094</v>
+        <v>40.26942982855918</v>
       </c>
       <c r="E66">
         <v>2</v>
@@ -2611,10 +2611,10 @@
         <v>71</v>
       </c>
       <c r="D67">
-        <v>56.26842720480796</v>
+        <v>8.969068329768112</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67" t="s">
         <v>29</v>
@@ -2640,7 +2640,7 @@
         <v>73</v>
       </c>
       <c r="D68">
-        <v>70.97469521067249</v>
+        <v>70.82400226177489</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -2669,10 +2669,10 @@
         <v>73</v>
       </c>
       <c r="D69">
-        <v>149.2739937838233</v>
+        <v>61.76264161675046</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69" t="s">
         <v>27</v>
@@ -2698,7 +2698,7 @@
         <v>73</v>
       </c>
       <c r="D70">
-        <v>41.96251417765986</v>
+        <v>7.737114786834848</v>
       </c>
       <c r="E70">
         <v>2</v>
@@ -2727,7 +2727,7 @@
         <v>75</v>
       </c>
       <c r="D71">
-        <v>749.4718399140905</v>
+        <v>749.675842484855</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -2756,7 +2756,7 @@
         <v>75</v>
       </c>
       <c r="D72">
-        <v>12.4864596753001</v>
+        <v>2.519589890469162</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -2785,7 +2785,7 @@
         <v>75</v>
       </c>
       <c r="D73">
-        <v>2.891222480621525</v>
+        <v>0.2984921335798238</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -2814,7 +2814,7 @@
         <v>77</v>
       </c>
       <c r="D74">
-        <v>977.7404030340294</v>
+        <v>977.9020420680006</v>
       </c>
       <c r="E74">
         <v>4</v>
@@ -2843,7 +2843,7 @@
         <v>77</v>
       </c>
       <c r="D75">
-        <v>26.25349444801241</v>
+        <v>9.69468052802868</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -2872,7 +2872,7 @@
         <v>77</v>
       </c>
       <c r="D76">
-        <v>5.164859774939202</v>
+        <v>1.40195898533738</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>79</v>
       </c>
       <c r="D77">
-        <v>103.4086049849635</v>
+        <v>103.6178445452273</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -2930,7 +2930,7 @@
         <v>79</v>
       </c>
       <c r="D78">
-        <v>167.0590109613497</v>
+        <v>93.37583632616321</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -2959,10 +2959,10 @@
         <v>79</v>
       </c>
       <c r="D79">
-        <v>26.22520367785448</v>
+        <v>5.175996558062884</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" t="s">
         <v>29</v>
@@ -2988,7 +2988,7 @@
         <v>81</v>
       </c>
       <c r="D80">
-        <v>548.0485353772867</v>
+        <v>545.3414059931569</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -3017,10 +3017,10 @@
         <v>81</v>
       </c>
       <c r="D81">
-        <v>241.2797722684294</v>
+        <v>85.64141124851885</v>
       </c>
       <c r="E81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F81" t="s">
         <v>27</v>
@@ -3046,10 +3046,10 @@
         <v>81</v>
       </c>
       <c r="D82">
-        <v>136.8689306232771</v>
+        <v>23.84431714789717</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F82" t="s">
         <v>29</v>
@@ -3102,13 +3102,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>70.97469521067249</v>
+        <v>70.82400226177489</v>
       </c>
       <c r="D2">
-        <v>129.4391267822657</v>
+        <v>129.5997411597099</v>
       </c>
       <c r="E2">
-        <v>0.5158938248144128</v>
+        <v>0.5159726265648682</v>
       </c>
       <c r="F2">
         <v>0.001</v>
@@ -3122,13 +3122,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>129.4391267822657</v>
+        <v>129.5997411597099</v>
       </c>
       <c r="D3">
-        <v>396.9867302289278</v>
+        <v>397.3376949619366</v>
       </c>
       <c r="E3">
-        <v>0.5158938248144128</v>
+        <v>0.5159726265648682</v>
       </c>
       <c r="F3">
         <v>0.001</v>
@@ -3142,13 +3142,13 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>396.9867302289278</v>
+        <v>397.3376949619366</v>
       </c>
       <c r="D4">
-        <v>761.6208923809667</v>
+        <v>760.7249254466265</v>
       </c>
       <c r="E4">
-        <v>0.5158938248144128</v>
+        <v>0.5159726265648682</v>
       </c>
       <c r="F4">
         <v>0.001</v>
@@ -3162,13 +3162,13 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>761.6208923809667</v>
+        <v>760.7249254466265</v>
       </c>
       <c r="D5">
-        <v>1212.045814592163</v>
+        <v>1212.290285512076</v>
       </c>
       <c r="E5">
-        <v>0.5158938248144128</v>
+        <v>0.5159726265648682</v>
       </c>
       <c r="F5">
         <v>0.001</v>
@@ -3182,13 +3182,13 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1212.045814592163</v>
+        <v>1212.290285512076</v>
       </c>
       <c r="D6">
-        <v>1782.370173642894</v>
+        <v>1783.747283001748</v>
       </c>
       <c r="E6">
-        <v>0.5158938248144128</v>
+        <v>0.5159726265648682</v>
       </c>
       <c r="F6">
         <v>0.001</v>
@@ -3202,16 +3202,16 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>5.639064915764338</v>
+        <v>1.690204324382488</v>
       </c>
       <c r="D7">
-        <v>67.25001813808062</v>
+        <v>18.1468302912281</v>
       </c>
       <c r="E7">
-        <v>0.004238851895810627</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="F7">
-        <v>0.285</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3222,16 +3222,16 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>67.25001813808062</v>
+        <v>18.1468302912281</v>
       </c>
       <c r="D8">
-        <v>135.6988243144004</v>
+        <v>61.76264161675046</v>
       </c>
       <c r="E8">
-        <v>0.004238851895810627</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="F8">
-        <v>0.285</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3242,16 +3242,16 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>135.6988243144004</v>
+        <v>61.76264161675046</v>
       </c>
       <c r="D9">
-        <v>196.5821881713077</v>
+        <v>99.65401283102314</v>
       </c>
       <c r="E9">
-        <v>0.004238851895810627</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="F9">
-        <v>0.285</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3262,16 +3262,16 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>196.5821881713077</v>
+        <v>99.65401283102314</v>
       </c>
       <c r="D10">
-        <v>324.9365537246113</v>
+        <v>155.9401117997334</v>
       </c>
       <c r="E10">
-        <v>0.004238851895810627</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="F10">
-        <v>0.285</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3282,16 +3282,16 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>324.9365537246113</v>
+        <v>155.9401117997334</v>
       </c>
       <c r="D11">
-        <v>498.3658184716266</v>
+        <v>227.7820589871915</v>
       </c>
       <c r="E11">
-        <v>0.004238851895810627</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="F11">
-        <v>0.285</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3302,16 +3302,16 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>2.347076112238387</v>
+        <v>0.2984921335798238</v>
       </c>
       <c r="D12">
-        <v>19.81032332703572</v>
+        <v>5.175996558062884</v>
       </c>
       <c r="E12">
-        <v>-0.006290288838290217</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="F12">
-        <v>0.326</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3322,16 +3322,16 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>19.81032332703572</v>
+        <v>5.175996558062884</v>
       </c>
       <c r="D13">
-        <v>41.96251417765986</v>
+        <v>15.4782711480731</v>
       </c>
       <c r="E13">
-        <v>-0.006290288838290217</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="F13">
-        <v>0.326</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3342,16 +3342,16 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>41.96251417765986</v>
+        <v>15.4782711480731</v>
       </c>
       <c r="D14">
-        <v>72.13933769774226</v>
+        <v>24.91581898666</v>
       </c>
       <c r="E14">
-        <v>-0.006290288838290217</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="F14">
-        <v>0.326</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3362,16 +3362,16 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>72.13933769774226</v>
+        <v>24.91581898666</v>
       </c>
       <c r="D15">
-        <v>98.44700785630522</v>
+        <v>42.66549156340798</v>
       </c>
       <c r="E15">
-        <v>-0.006290288838290217</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="F15">
-        <v>0.326</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3382,16 +3382,16 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>98.44700785630522</v>
+        <v>42.66549156340798</v>
       </c>
       <c r="D16">
-        <v>136.8689306232771</v>
+        <v>72.69112413964704</v>
       </c>
       <c r="E16">
-        <v>-0.006290288838290217</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="F16">
-        <v>0.326</v>
+        <v>0.243</v>
       </c>
     </row>
   </sheetData>
